--- a/04_Figures/F05_classification/modules/training/HR_LR/svm/c_data/results.xlsx
+++ b/04_Figures/F05_classification/modules/training/HR_LR/svm/c_data/results.xlsx
@@ -521,13 +521,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.125</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.319238547712681</v>
+        <v>0.58057709233591</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
@@ -556,22 +556,22 @@
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.319238547712681</v>
+        <v>0.58057709233591</v>
       </c>
       <c r="K3" t="n">
-        <v>0.671641791044776</v>
+        <v>0.417910447761194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.314270833333333</v>
+        <v>0.3065625</v>
       </c>
       <c r="M3" t="n">
-        <v>0.274220838450523</v>
+        <v>0.280741618978883</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>0.229166666666667</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>0.145833333333333</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -638,7 +638,7 @@
         <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>0.291666666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +654,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.583333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -662,7 +662,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.395833333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6875</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -678,7 +678,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0625</v>
+        <v>0.291666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -686,7 +686,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>0.479166666666667</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.229166666666667</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -718,7 +718,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.229166666666667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="18">
@@ -734,7 +734,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0625</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="20">
@@ -742,7 +742,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>0.541666666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -750,7 +750,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>0.229166666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="22">
@@ -758,7 +758,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6875</v>
+        <v>0.708333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -766,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="24">
@@ -774,7 +774,7 @@
         <v>15</v>
       </c>
       <c r="B24" t="n">
-        <v>0.875</v>
+        <v>0.729166666666667</v>
       </c>
     </row>
     <row r="25">
@@ -782,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>0.458333333333333</v>
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="B26" t="n">
-        <v>0.145833333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27">
@@ -798,7 +798,7 @@
         <v>15</v>
       </c>
       <c r="B27" t="n">
-        <v>0.104166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -814,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="B29" t="n">
-        <v>0.333333333333333</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -822,7 +822,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="n">
-        <v>0.791666666666667</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="31">
@@ -830,7 +830,7 @@
         <v>15</v>
       </c>
       <c r="B31" t="n">
-        <v>0.854166666666667</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="32">
@@ -838,7 +838,7 @@
         <v>15</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
@@ -854,7 +854,7 @@
         <v>15</v>
       </c>
       <c r="B34" t="n">
-        <v>0.645833333333333</v>
+        <v>0.708333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -862,7 +862,7 @@
         <v>15</v>
       </c>
       <c r="B35" t="n">
-        <v>0.604166666666667</v>
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -870,7 +870,7 @@
         <v>15</v>
       </c>
       <c r="B36" t="n">
-        <v>0.25</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="B37" t="n">
-        <v>0.333333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -886,7 +886,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="39">
@@ -894,7 +894,7 @@
         <v>15</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="40">
@@ -902,7 +902,7 @@
         <v>15</v>
       </c>
       <c r="B40" t="n">
-        <v>0.6875</v>
+        <v>0.708333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -910,7 +910,7 @@
         <v>15</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="42">
@@ -918,7 +918,7 @@
         <v>15</v>
       </c>
       <c r="B42" t="n">
-        <v>0.229166666666667</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="43">
@@ -926,7 +926,7 @@
         <v>15</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="44">
@@ -934,7 +934,7 @@
         <v>15</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="45">
@@ -942,7 +942,7 @@
         <v>15</v>
       </c>
       <c r="B45" t="n">
-        <v>0.166666666666667</v>
+        <v>0.145833333333333</v>
       </c>
     </row>
     <row r="46">
@@ -950,7 +950,7 @@
         <v>15</v>
       </c>
       <c r="B46" t="n">
-        <v>0.354166666666667</v>
+        <v>0.520833333333333</v>
       </c>
     </row>
     <row r="47">
@@ -958,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5625</v>
+        <v>0.770833333333333</v>
       </c>
     </row>
     <row r="48">
@@ -966,7 +966,7 @@
         <v>15</v>
       </c>
       <c r="B48" t="n">
-        <v>0.833333333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="49">
@@ -982,7 +982,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>0.25</v>
+        <v>0.291666666666667</v>
       </c>
     </row>
     <row r="51">
@@ -990,7 +990,7 @@
         <v>15</v>
       </c>
       <c r="B51" t="n">
-        <v>0.895833333333333</v>
+        <v>0.916666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -998,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1006,7 +1006,7 @@
         <v>15</v>
       </c>
       <c r="B53" t="n">
-        <v>0.208333333333333</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1014,7 +1014,7 @@
         <v>15</v>
       </c>
       <c r="B54" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
@@ -1022,7 +1022,7 @@
         <v>15</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="56">
@@ -1030,7 +1030,7 @@
         <v>15</v>
       </c>
       <c r="B56" t="n">
-        <v>0.395833333333333</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="57">
@@ -1046,7 +1046,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="n">
-        <v>0.166666666666667</v>
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="59">
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="60">
@@ -1062,7 +1062,7 @@
         <v>15</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="61">
@@ -1078,7 +1078,7 @@
         <v>15</v>
       </c>
       <c r="B62" t="n">
-        <v>0.479166666666667</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="63">
@@ -1086,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="B63" t="n">
-        <v>0.104166666666667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="64">
@@ -1094,7 +1094,7 @@
         <v>15</v>
       </c>
       <c r="B64" t="n">
-        <v>0.270833333333333</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="65">
@@ -1102,7 +1102,7 @@
         <v>15</v>
       </c>
       <c r="B65" t="n">
-        <v>0.395833333333333</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="66">
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="67">
@@ -1118,7 +1118,7 @@
         <v>15</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1875</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="68">
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="69">
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1142,7 +1142,7 @@
         <v>15</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="71">
@@ -1150,7 +1150,7 @@
         <v>15</v>
       </c>
       <c r="B71" t="n">
-        <v>0.458333333333333</v>
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="72">
@@ -1158,7 +1158,7 @@
         <v>15</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1166,7 +1166,7 @@
         <v>15</v>
       </c>
       <c r="B73" t="n">
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="74">
@@ -1182,7 +1182,7 @@
         <v>15</v>
       </c>
       <c r="B75" t="n">
-        <v>0.375</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="76">
@@ -1190,7 +1190,7 @@
         <v>15</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="77">
@@ -1198,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="B77" t="n">
-        <v>0.708333333333333</v>
+        <v>0.791666666666667</v>
       </c>
     </row>
     <row r="78">
@@ -1206,7 +1206,7 @@
         <v>15</v>
       </c>
       <c r="B78" t="n">
-        <v>0.770833333333333</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="79">
@@ -1214,7 +1214,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="n">
-        <v>0.416666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="80">
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
       <c r="B80" t="n">
-        <v>0.479166666666667</v>
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="81">
@@ -1230,7 +1230,7 @@
         <v>15</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="82">
@@ -1238,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="B82" t="n">
-        <v>0.8125</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="84">
@@ -1254,7 +1254,7 @@
         <v>15</v>
       </c>
       <c r="B84" t="n">
-        <v>0.145833333333333</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="85">
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="B85" t="n">
-        <v>0.375</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="86">
@@ -1270,7 +1270,7 @@
         <v>15</v>
       </c>
       <c r="B86" t="n">
-        <v>0.104166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1278,7 +1278,7 @@
         <v>15</v>
       </c>
       <c r="B87" t="n">
-        <v>0.104166666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="88">
@@ -1294,7 +1294,7 @@
         <v>15</v>
       </c>
       <c r="B89" t="n">
-        <v>0.395833333333333</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="90">
@@ -1302,7 +1302,7 @@
         <v>15</v>
       </c>
       <c r="B90" t="n">
-        <v>0.208333333333333</v>
+        <v>0.395833333333333</v>
       </c>
     </row>
     <row r="91">
@@ -1310,7 +1310,7 @@
         <v>15</v>
       </c>
       <c r="B91" t="n">
-        <v>0.645833333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="92">
@@ -1318,7 +1318,7 @@
         <v>15</v>
       </c>
       <c r="B92" t="n">
-        <v>0.25</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="93">
@@ -1326,7 +1326,7 @@
         <v>15</v>
       </c>
       <c r="B93" t="n">
-        <v>0.708333333333333</v>
+        <v>0.604166666666667</v>
       </c>
     </row>
     <row r="94">
@@ -1342,7 +1342,7 @@
         <v>15</v>
       </c>
       <c r="B95" t="n">
-        <v>0.375</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="96">
@@ -1358,7 +1358,7 @@
         <v>15</v>
       </c>
       <c r="B97" t="n">
-        <v>0.145833333333333</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="98">
@@ -1366,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="99">
@@ -1374,7 +1374,7 @@
         <v>15</v>
       </c>
       <c r="B99" t="n">
-        <v>0.208333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
       <c r="B100" t="n">
-        <v>0.25</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="101">
@@ -1390,7 +1390,7 @@
         <v>15</v>
       </c>
       <c r="B101" t="n">
-        <v>0.770833333333333</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="102">
@@ -1398,7 +1398,7 @@
         <v>15</v>
       </c>
       <c r="B102" t="n">
-        <v>0.645833333333333</v>
+        <v>0.479166666666667</v>
       </c>
     </row>
     <row r="103">
@@ -1414,7 +1414,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="n">
-        <v>0.416666666666667</v>
+        <v>0.479166666666667</v>
       </c>
     </row>
     <row r="105">
@@ -1422,7 +1422,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="n">
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="106">
@@ -1430,7 +1430,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0833333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -1438,7 +1438,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="n">
-        <v>0.333333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="108">
@@ -1446,7 +1446,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="n">
-        <v>0.145833333333333</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="109">
@@ -1454,7 +1454,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="n">
-        <v>0.125</v>
+        <v>0.270833333333333</v>
       </c>
     </row>
     <row r="110">
@@ -1470,7 +1470,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="n">
-        <v>0.333333333333333</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="112">
@@ -1478,7 +1478,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="n">
-        <v>0.583333333333333</v>
+        <v>0.458333333333333</v>
       </c>
     </row>
     <row r="113">
@@ -1486,7 +1486,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1494,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="n">
-        <v>0.145833333333333</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="115">
@@ -1502,7 +1502,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="n">
-        <v>0.1875</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="116">
@@ -1510,7 +1510,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="n">
-        <v>0.833333333333333</v>
+        <v>0.770833333333333</v>
       </c>
     </row>
     <row r="117">
@@ -1518,7 +1518,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="118">
@@ -1526,7 +1526,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="n">
-        <v>0.291666666666667</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="119">
@@ -1534,7 +1534,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="120">
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="n">
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="122">
@@ -1558,7 +1558,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="n">
-        <v>0.3125</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="123">
@@ -1566,7 +1566,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="n">
-        <v>0.770833333333333</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="124">
@@ -1574,7 +1574,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="125">
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="126">
@@ -1590,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="127">
@@ -1598,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.229166666666667</v>
       </c>
     </row>
     <row r="128">
@@ -1622,7 +1622,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="n">
-        <v>0.625</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="131">
@@ -1630,7 +1630,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="n">
-        <v>0.333333333333333</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="132">
@@ -1638,7 +1638,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="n">
-        <v>0.229166666666667</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="133">
@@ -1654,7 +1654,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1670,7 +1670,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="n">
-        <v>0.458333333333333</v>
+        <v>0.520833333333333</v>
       </c>
     </row>
     <row r="137">
@@ -1678,7 +1678,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="n">
-        <v>0.333333333333333</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="138">
@@ -1686,7 +1686,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="n">
-        <v>0.979166666666667</v>
+        <v>0.916666666666667</v>
       </c>
     </row>
     <row r="139">
@@ -1702,7 +1702,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="n">
-        <v>0.1875</v>
+        <v>0.145833333333333</v>
       </c>
     </row>
     <row r="141">
@@ -1710,7 +1710,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="n">
-        <v>0.229166666666667</v>
+        <v>0.395833333333333</v>
       </c>
     </row>
     <row r="142">
@@ -1718,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="n">
-        <v>0.4375</v>
+        <v>0.458333333333333</v>
       </c>
     </row>
     <row r="143">
@@ -1726,7 +1726,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.145833333333333</v>
       </c>
     </row>
     <row r="144">
@@ -1734,7 +1734,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="146">
@@ -1750,7 +1750,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="n">
-        <v>0.791666666666667</v>
+        <v>0.729166666666667</v>
       </c>
     </row>
     <row r="147">
@@ -1758,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="n">
-        <v>0.479166666666667</v>
+        <v>0.458333333333333</v>
       </c>
     </row>
     <row r="148">
@@ -1766,7 +1766,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="149">
@@ -1782,7 +1782,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="n">
-        <v>0.541666666666667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
@@ -1790,7 +1790,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="n">
-        <v>0.104166666666667</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="152">
@@ -1798,7 +1798,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="153">
@@ -1806,7 +1806,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="n">
-        <v>0.458333333333333</v>
+        <v>0.520833333333333</v>
       </c>
     </row>
     <row r="154">
@@ -1814,7 +1814,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="155">
@@ -1830,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="n">
-        <v>0.208333333333333</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="157">
@@ -1838,7 +1838,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="n">
-        <v>0.416666666666667</v>
+        <v>0.520833333333333</v>
       </c>
     </row>
     <row r="158">
@@ -1846,7 +1846,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="159">
@@ -1854,7 +1854,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="n">
-        <v>0.395833333333333</v>
+        <v>0.604166666666667</v>
       </c>
     </row>
     <row r="160">
@@ -1862,7 +1862,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0833333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -1870,7 +1870,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="n">
-        <v>0.270833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -1878,7 +1878,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="n">
-        <v>0.229166666666667</v>
+        <v>0.0833333333333333</v>
       </c>
     </row>
     <row r="163">
@@ -1886,7 +1886,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="n">
-        <v>0.5625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="164">
@@ -1894,7 +1894,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="n">
-        <v>0.270833333333333</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="165">
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="n">
-        <v>0.791666666666667</v>
+        <v>0.770833333333333</v>
       </c>
     </row>
     <row r="166">
@@ -1910,7 +1910,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="n">
-        <v>0.791666666666667</v>
+        <v>0.729166666666667</v>
       </c>
     </row>
     <row r="167">
@@ -1918,7 +1918,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="n">
-        <v>0.895833333333333</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="168">
@@ -1926,7 +1926,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="n">
-        <v>0.291666666666667</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="169">
@@ -1934,7 +1934,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="n">
-        <v>0.4375</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="170">
@@ -1942,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="n">
-        <v>0.208333333333333</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="171">
@@ -1958,7 +1958,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="173">
@@ -1966,7 +1966,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="174">
@@ -1974,7 +1974,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="n">
-        <v>0.104166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -1990,7 +1990,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.208333333333333</v>
       </c>
     </row>
     <row r="177">
@@ -2006,7 +2006,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0208333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="179">
@@ -2014,7 +2014,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="n">
-        <v>0.208333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -2022,7 +2022,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="n">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="181">
@@ -2030,7 +2030,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="182">
@@ -2038,7 +2038,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="n">
-        <v>0.229166666666667</v>
+        <v>0.291666666666667</v>
       </c>
     </row>
     <row r="183">
@@ -2046,7 +2046,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="n">
-        <v>0.291666666666667</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="184">
@@ -2054,7 +2054,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="n">
-        <v>0.270833333333333</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="185">
@@ -2070,7 +2070,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="n">
-        <v>0.916666666666667</v>
+        <v>0.791666666666667</v>
       </c>
     </row>
     <row r="187">
@@ -2078,7 +2078,7 @@
         <v>15</v>
       </c>
       <c r="B187" t="n">
-        <v>0.229166666666667</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="188">
@@ -2086,7 +2086,7 @@
         <v>15</v>
       </c>
       <c r="B188" t="n">
-        <v>0.625</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="189">
@@ -2102,7 +2102,7 @@
         <v>15</v>
       </c>
       <c r="B190" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="191">
@@ -2110,7 +2110,7 @@
         <v>15</v>
       </c>
       <c r="B191" t="n">
-        <v>0.354166666666667</v>
+        <v>0.0208333333333333</v>
       </c>
     </row>
     <row r="192">
@@ -2118,7 +2118,7 @@
         <v>15</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="193">
@@ -2126,7 +2126,7 @@
         <v>15</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -2134,7 +2134,7 @@
         <v>15</v>
       </c>
       <c r="B194" t="n">
-        <v>0.104166666666667</v>
+        <v>0.0416666666666667</v>
       </c>
     </row>
     <row r="195">
@@ -2142,7 +2142,7 @@
         <v>15</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="196">
@@ -2150,7 +2150,7 @@
         <v>15</v>
       </c>
       <c r="B196" t="n">
-        <v>0.520833333333333</v>
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="197">
@@ -2166,7 +2166,7 @@
         <v>15</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="199">
@@ -2174,7 +2174,7 @@
         <v>15</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="200">
@@ -2182,7 +2182,7 @@
         <v>15</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="201">
@@ -2190,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="B201" t="n">
-        <v>0.104166666666667</v>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.313580949989481</v>
+        <v>0.393694667690252</v>
       </c>
     </row>
     <row r="3">
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.192556442975301</v>
+        <v>0.340929986560322</v>
       </c>
     </row>
     <row r="4">
@@ -2257,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.383627382205944</v>
+        <v>0.369074416333514</v>
       </c>
     </row>
     <row r="5">
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.137607615374517</v>
+        <v>0.0388359311802722</v>
       </c>
     </row>
     <row r="6">
@@ -2285,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.378903316832241</v>
+        <v>0.371847694901771</v>
       </c>
     </row>
     <row r="7">
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.406058154806789</v>
+        <v>0.496336444336834</v>
       </c>
     </row>
     <row r="8">
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.429166899192739</v>
+        <v>0.409452464997852</v>
       </c>
     </row>
     <row r="9">
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.440964963880034</v>
+        <v>0.4589017209804</v>
       </c>
     </row>
     <row r="10">
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.452808220577847</v>
+        <v>0.483965806276399</v>
       </c>
     </row>
     <row r="11">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.35463558821759</v>
+        <v>0.346466217738479</v>
       </c>
     </row>
     <row r="12">
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.460642884136459</v>
+        <v>0.459532007102441</v>
       </c>
     </row>
     <row r="13">
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.554637545433836</v>
+        <v>0.459880431539162</v>
       </c>
     </row>
     <row r="14">
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.346894620878308</v>
+        <v>0.342720154618053</v>
       </c>
     </row>
     <row r="15">
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.616246059691834</v>
+        <v>0.55013731157598</v>
       </c>
     </row>
   </sheetData>
